--- a/docs/TEST_CASES.xlsx
+++ b/docs/TEST_CASES.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1471,6 +1471,154 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>TC-027</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>P1-3</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>tests/unit/test_offline_harness.py</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>test_offline_env_vars_active</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Verify offline environment variables set in conftest.py</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Harness / Unit</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>TC-028</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>P1-3</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>tests/unit/test_offline_harness.py</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>test_auth_fixtures_generate_valid_tokens</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Verify admin, agent, viewer auth headers and token signatures</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Harness / Security</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>TC-029</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>P1-3</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>tests/unit/test_offline_harness.py</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>test_client_fixture</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Verify global synchronous TestClient fixture connects to app</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Harness / Integration</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>TC-030</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>P1-3</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>tests/unit/test_offline_harness.py</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>test_async_client_fixture</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Verify global asynchronous AsyncClient fixture with ASGI transport</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Harness / Integration</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/TEST_CASES.xlsx
+++ b/docs/TEST_CASES.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1619,6 +1619,191 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>TC-031</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>P1-4</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>tests/deployment/test_env_example.py</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>test_env_example_exists</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Verify .env.example exists at repository root</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Deployment / Hygiene</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>TC-032</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>P1-4</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>tests/deployment/test_env_example.py</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>test_env_example_covers_all_settings_fields</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Verify .env.example covers 100% of Settings model fields</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Deployment / Compliance</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>TC-033</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>P1-4</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>tests/deployment/test_env_example.py</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>test_no_committed_env_file</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Verify .env is git-ignored and never tracked in Git</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Security / Hygiene</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>TC-034</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>P1-4</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>tests/deployment/test_env_example.py</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>test_makefile_exists_and_contains_targets</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Verify Makefile defines setup, test, lint, backend, demo targets</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Build / CLI</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>TC-035</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>P1-4</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>tests/deployment/test_env_example.py</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>test_env_example_contains_safe_placeholders_only</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Verify .env.example contains zero live cloud or LLM API keys</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Security / Compliance</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/TEST_CASES.xlsx
+++ b/docs/TEST_CASES.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Test Cases" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Cases" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1804,6 +1804,561 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>TC-036</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>P2-1</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>tests/unit/test_entities.py</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>test_category_enum_contains_exact_ten_categories</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Assert CategoryEnum defines exactly 10 canonical categories from CLAUDE.md section 5</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>TC-037</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>P2-1</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>tests/unit/test_entities.py</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>test_ticket_status_enum</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Assert TicketStatusEnum defines all 7 lifecycle statuses</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>TC-038</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>P2-1</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>tests/unit/test_entities.py</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>test_severity_enum</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Assert SeverityEnum defines low/medium/high/critical urgency levels</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>TC-039</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>P2-1</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>tests/unit/test_entities.py</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>test_channel_enum</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Assert ChannelEnum defines email/chat/web/api intake channels</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>TC-040</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>P2-1</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>tests/unit/test_entities.py</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>test_role_enum_and_hierarchy</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Assert RoleEnum defines viewer/agent/admin RBAC roles</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>TC-041</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>P2-1</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>tests/unit/test_entities.py</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>test_customer_plan_enum</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Assert CustomerPlanEnum defines free/pro/business/enterprise tiers</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>TC-042</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>P2-1</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>tests/unit/test_entities.py</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>test_approval_status_enum</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Assert ApprovalStatusEnum defines pending/approved/rejected statuses</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>TC-043</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>P2-1</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>tests/unit/test_entities.py</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>test_memory_type_enum</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Assert MemoryTypeEnum defines past_issue/troubleshooting/note/preference</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>TC-044</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>P2-1</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>tests/unit/test_entities.py</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>test_workflow_status_enum</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Assert WorkflowStatusEnum defines all 6 workflow lifecycle statuses</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>TC-045</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>P2-1</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>tests/unit/test_entities.py</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>test_table_registry_contains_all_sixteen_tables</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Assert SQLAlchemy Base metadata registers all 16 tables from CLAUDE.md section 6</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>TC-046</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>P2-1</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>tests/unit/test_entities.py</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>test_create_customer_and_workspace</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Verify Customer and Workspace insertion and foreign key relationship</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>TC-047</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>P2-1</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>tests/unit/test_entities.py</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>test_create_ticket_with_messages</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Verify Ticket and TicketMessage persistence with default statuses and cascades</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>TC-048</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>P2-1</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>tests/unit/test_entities.py</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>test_workflow_run_and_approval_request</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Verify WorkflowRun JSON state handling and ApprovalRequest entity persistence</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>TC-049</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>P2-1</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>tests/unit/test_entities.py</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>test_customer_memory_and_audit_log</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Verify CustomerMemory note persistence and AuditLog state-change logging</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>TC-050</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>P2-1</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>tests/unit/test_entities.py</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>test_base_model_uuid_and_timestamps</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Verify default 36-char UUID4 generation and UTC timestamps on model instantiation</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/TEST_CASES.xlsx
+++ b/docs/TEST_CASES.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2359,6 +2359,376 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>TC-051</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>P2-2</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>tests/unit/test_postgres_schema.py</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>test_schema_files_exist</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Verify schema.sql, rls_policies.sql, and initial migration exist</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>TC-052</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>P2-2</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>tests/unit/test_postgres_schema.py</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>test_schema_defines_all_sixteen_tables</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Assert database/schema.sql defines all 16 tables matching SQLAlchemy metadata</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>TC-053</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>P2-2</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>tests/unit/test_postgres_schema.py</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>test_schema_updated_at_trigger_function</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Verify set_updated_at trigger is applied to all 15 timestamped tables and excluded from audit_logs</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>TC-054</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>P2-2</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>tests/unit/test_postgres_schema.py</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>test_foreign_key_cascade_rules</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Verify foreign key ON DELETE CASCADE on child records and ON DELETE SET NULL on profiles</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>TC-055</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>P2-2</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>tests/unit/test_postgres_schema.py</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>test_audit_logs_has_no_foreign_keys</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Verify audit_logs table has zero foreign key dependencies to ensure permanent immutability</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>TC-056</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>P2-2</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>tests/unit/test_postgres_schema.py</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>test_rls_enabled_on_all_tables</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Verify Row Level Security is explicitly enabled on all 16 tables in rls_policies.sql</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>TC-057</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>P2-2</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>tests/unit/test_postgres_schema.py</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>test_service_role_bypass_policies</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Verify service_role policies exist on all 16 tables for backend administrative access</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>TC-058</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>P2-2</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>tests/unit/test_postgres_schema.py</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>test_role_based_policies_exist</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Verify authenticated role-based policies restrict mutations to agent and admin roles</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>TC-059</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>P2-2</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>tests/unit/test_postgres_schema.py</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>test_initial_migration_contains_schema_and_rls</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Verify 0001_initial_schema.sql contains full transactional schema DDL and RLS</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>TC-060</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>P2-2</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>tests/unit/test_postgres_schema.py</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>test_migration_naming_convention</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Verify all migration files follow the 000N_&lt;name&gt;.sql naming format</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/TEST_CASES.xlsx
+++ b/docs/TEST_CASES.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Cases" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Test Cases" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2729,6 +2729,413 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>TC-061</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>P2-3</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>tests/unit/test_repositories.py</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>test_database_engine_and_session_factory</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Verify async database engine creation, sessionmaker singleton, and async session generator lifecycle</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>TC-062</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>P2-3</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>tests/unit/test_repositories.py</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>test_create_tables_utility</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Verify create_tables initializes all 16 tables in SQLite demo/test database</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>TC-063</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>P2-3</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>tests/unit/test_repositories.py</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>test_base_repository_crud_operations</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Verify generic BaseRepository CRUD (create, get, list with offset/limit, count, update, delete)</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>TC-064</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>P2-3</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>tests/unit/test_repositories.py</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>test_customer_and_workspace_queries</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Verify CustomerRepository email/profile queries, eager-loading workspaces and subscriptions, and WorkspaceRepository slug queries</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>TC-065</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>P2-3</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>tests/unit/test_repositories.py</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>test_create_ticket_with_initial_message_atomic</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Verify atomic creation of Ticket and initial customer TicketMessage within a single transaction</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>TC-066</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>P2-3</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>tests/unit/test_repositories.py</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>test_get_ticket_with_messages_chronological_order</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Verify TicketRepository eager-loads conversation messages ordered chronologically (created_at ASC)</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>TC-067</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>P2-3</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>tests/unit/test_repositories.py</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>test_list_tickets_with_filters_and_pagination</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Verify TicketRepository list filtering by status, severity, category, customer_id with pagination and total count</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>TC-068</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>P2-3</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>tests/unit/test_repositories.py</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>test_update_ticket_status_and_assignment</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Verify TicketRepository update_status and assign_agent operations</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>TC-069</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>P2-3</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>tests/unit/test_repositories.py</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>test_approval_repository_lifecycle</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Verify ApprovalRepository pending queue queries and status transition recording (decided_by, rejection_reason, decided_at)</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>TC-070</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>P2-3</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>tests/unit/test_repositories.py</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>test_customer_memory_recall_limit</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Verify CustomerMemoryRepository append and recent notes recall capped at limit (top 10 newest first)</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>TC-071</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>P2-3</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>tests/unit/test_repositories.py</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>test_sql_injection_resilience_in_repository_filters</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Penetration test: verify SQL injection payloads in filter parameters are parameterized and treated as literal values</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/TEST_CASES.xlsx
+++ b/docs/TEST_CASES.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3136,6 +3136,302 @@
         </is>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>TC-072</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>P2-4</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>tests/unit/test_seed_service.py</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>test_sample_data_files_exist_and_valid_json</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Verify existence and valid JSON array formatting of all required sample dataset files</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>TC-073</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>P2-4</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>tests/unit/test_seed_service.py</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>test_customers_cover_all_plans_and_count_is_eight</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Verify sample_data/customers.json contains exactly 8 customers covering all 4 subscription plans</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>TC-074</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>P2-4</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>tests/unit/test_seed_service.py</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>test_tickets_cover_thirteen_demo_scenarios</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Verify sample_data/tickets.json contains exactly 13 demo tickets matching CD-1001 through CD-1013</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>TC-075</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>P2-4</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>tests/unit/test_seed_service.py</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>test_knowledge_base_articles_count_and_frontmatter</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Verify sample_data/knowledge_base contains 15 markdown articles with valid YAML frontmatter covering all 10 categories</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>TC-076</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>P2-4</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>tests/unit/test_seed_service.py</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>test_seed_sql_file_exists_and_valid</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Verify database/seed.sql contains transactional SQL INSERT statements for profiles, customers, workspaces, products, articles, and tickets</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>TC-077</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>P2-4</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>tests/unit/test_seed_service.py</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>test_bootstrap_demo_data_populates_empty_database</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Verify bootstrap_demo_data service populates all sample entities into an empty database</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>TC-078</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>P2-4</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>tests/unit/test_seed_service.py</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>test_bootstrap_demo_data_is_idempotent</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Verify bootstrap_demo_data skips or returns gracefully on populated database without duplicating rows</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>TC-079</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>P2-4</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>tests/unit/test_seed_service.py</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>test_security_sanitization_in_sample_data</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Penetration test: verify sample datasets and seed.sql contain zero live API keys, secrets, or passwords</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/TEST_CASES.xlsx
+++ b/docs/TEST_CASES.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Test Cases" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Cases" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3432,6 +3432,820 @@
         </is>
       </c>
     </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>TC-080</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>P3-1</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>tests/unit/test_security.py</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>test_create_access_token_default_expiry</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Verify JWT generation embeds sub, email, role, and defaults to 8-hour expiry</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>TC-081</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>P3-1</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>tests/unit/test_security.py</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>test_create_access_token_custom_expiry</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Verify JWT generation respects custom timedelta expiration window</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>TC-082</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>P3-1</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>tests/unit/test_security.py</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>test_decode_access_token_valid</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Verify decoding valid HS256 JWT returns exact payload claims</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>TC-083</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>P3-1</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>tests/unit/test_security.py</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>test_decode_access_token_expired_raises_401</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Verify decoding expired token raises HTTP 401 with standard error detail (AC-062)</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>TC-084</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>P3-1</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>tests/unit/test_security.py</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>test_decode_access_token_tampered_signature_raises_401</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Verify token signed with untrusted secret key raises HTTP 401</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>TC-085</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>P3-1</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>tests/unit/test_security.py</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>test_decode_access_token_none_algorithm_attack_rejected</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Penetration test: reject unsigned tokens using none algorithm (CWE-345)</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>TC-086</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>P3-1</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>tests/unit/test_security.py</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>test_decode_access_token_malformed_string_raises_401</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Verify malformed and unparseable JWT strings raise HTTP 401</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>TC-087</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>P3-1</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>tests/unit/test_security.py</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>test_get_current_user_valid</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Verify get_current_user dependency extracts AuthenticatedUser from valid token</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>TC-088</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>P3-1</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>tests/unit/test_security.py</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>test_get_current_user_missing_credentials_raises_401</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Verify missing Authorization header raises HTTP 401 with WWW-Authenticate header</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>TC-089</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>P3-1</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>tests/unit/test_security.py</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>test_get_current_user_missing_required_claims_raises_401</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Verify token missing mandatory sub, email, or role claims raises HTTP 401</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>TC-090</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>P3-1</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>tests/unit/test_security.py</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>test_get_current_user_invalid_role_claim_raises_401</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Verify token with unmapped or invalid role claim raises HTTP 401</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>TC-091</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>P3-1</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>tests/unit/test_security.py</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>test_role_hierarchy_values</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Verify numerical role hierarchy strictly enforces viewer (1) &lt; agent (2) &lt; admin (3) (AC-061)</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>TC-092</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>P3-1</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>tests/unit/test_security.py</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>test_require_role_viewer_access</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Verify require_role(viewer) permits viewer, agent, and admin actors</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>TC-093</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>P3-1</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>tests/unit/test_security.py</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>test_require_role_agent_access</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Verify require_role(agent) permits agent and admin; rejects viewer with HTTP 403</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>TC-094</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>P3-1</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>tests/unit/test_security.py</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>test_require_role_admin_access</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Verify require_role(admin) permits admin only; rejects agent and viewer with HTTP 403</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>TC-095</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>P3-1</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>tests/unit/test_security.py</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>test_require_role_accepts_string_or_enum</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Verify require_role normalizes string role names and canonical RoleEnum values</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>TC-096</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>P3-1</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>tests/unit/test_security.py</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>test_require_role_invalid_role_raises_value_error</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Verify initializing require_role with non-existent role raises ValueError</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>TC-097</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>P3-1</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>tests/unit/test_security.py</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>test_public_endpoint_accessible_without_auth</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Verify un-gated public endpoints return 200 without Authorization header</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>TC-098</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>P3-1</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>tests/unit/test_security.py</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>test_protected_endpoints_reject_unauthenticated</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Verify all protected endpoints reject unauthenticated calls with HTTP 401</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>TC-099</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>P3-1</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>tests/unit/test_security.py</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>test_viewer_access_boundaries</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Verify viewer token accesses viewer endpoint but is blocked (HTTP 403) from agent and admin</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>TC-100</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>P3-1</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>tests/unit/test_security.py</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>test_agent_access_boundaries</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Verify agent token accesses viewer and agent endpoints but is blocked (HTTP 403) from admin</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>TC-101</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>P3-1</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>tests/unit/test_security.py</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>test_admin_access_boundaries</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Verify admin token has full access across viewer, agent, and admin endpoints</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/TEST_CASES.xlsx
+++ b/docs/TEST_CASES.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G102"/>
+  <dimension ref="A1:G117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4246,6 +4246,561 @@
         </is>
       </c>
     </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>TC-102</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>P3-2</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>tests/api/test_auth.py</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>test_login_admin_success</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Verify admin demo login issues valid HS256 token and user profile</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>TC-103</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>P3-2</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>tests/api/test_auth.py</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>test_login_agent_success</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Verify agent demo login issues valid token with agent role</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>TC-104</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>P3-2</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>tests/api/test_auth.py</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>test_login_viewer_success</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Verify viewer demo login issues valid token with viewer role</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>TC-105</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>P3-2</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>tests/api/test_auth.py</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>test_login_case_insensitive_email</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Verify login email matching normalizes case insensitively</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>TC-106</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>P3-2</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>tests/api/test_auth.py</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>test_login_unknown_email_returns_401</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Verify unrecognized credentials return HTTP 401 with standard error envelope</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>TC-107</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>P3-2</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>tests/api/test_auth.py</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>test_login_malformed_body_returns_422</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Verify malformed or missing body parameters return HTTP 422</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>TC-108</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>P3-2</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>tests/api/test_auth.py</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>test_get_demo_tokens_success_in_demo_mode</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Verify GET /api/v1/auth/demo-tokens returns valid pre-generated tokens for all 3 roles</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>TC-109</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>P3-2</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>tests/api/test_auth.py</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>test_get_demo_tokens_disabled_in_production</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Penetration test: verify demo tokens endpoint is blocked with HTTP 403 when DEMO_MODE=False</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>TC-110</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>P3-2</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>tests/api/test_auth.py</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>test_get_me_success_with_admin_token</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Verify GET /api/v1/auth/me returns authenticated admin user profile</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>TC-111</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>P3-2</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>tests/api/test_auth.py</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>test_get_me_success_with_agent_token</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Verify GET /api/v1/auth/me returns authenticated agent user profile</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>TC-112</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>P3-2</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>tests/api/test_auth.py</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>test_get_me_unauthenticated_returns_401</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Verify GET /api/v1/auth/me without Bearer token returns HTTP 401</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>TC-113</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>P3-2</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>tests/api/test_auth.py</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>test_get_me_invalid_token_returns_401</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Verify GET /api/v1/auth/me with invalid token returns HTTP 401</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>TC-114</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>P3-2</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>tests/api/test_auth.py</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>test_refresh_token_success</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Verify POST /api/v1/auth/refresh returns renewed 8-hour access token</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>TC-115</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>P3-2</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>tests/api/test_auth.py</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>test_refresh_token_unauthenticated_returns_401</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Verify POST /api/v1/auth/refresh without token returns HTTP 401</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>TC-116</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>P3-2</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>tests/api/test_auth.py</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>test_login_and_access_workflow</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>End-to-end integration: login, query profile, refresh token, and re-query profile</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/TEST_CASES.xlsx
+++ b/docs/TEST_CASES.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G117"/>
+  <dimension ref="A1:G128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4801,6 +4801,413 @@
         </is>
       </c>
     </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>TC-117</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>P3-3</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>tests/unit/test_redis.py</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>test_get_redis_client_fake</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Verify get_redis_client returns functional async FakeRedis in offline mode</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>TC-118</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>P3-3</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>tests/unit/test_redis.py</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>test_get_redis_client_singleton</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Verify get_redis_client manages single active connection instance</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>TC-119</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>P3-3</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>tests/unit/test_redis.py</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>test_close_redis_client</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Verify close_redis_client closes connection and clears singleton reference</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>TC-120</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>P3-3</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>tests/unit/test_redis.py</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>test_probe_redis_success</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Verify probe_redis returns True when ping to Redis server succeeds</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>TC-121</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>P3-3</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>tests/unit/test_redis.py</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>test_probe_redis_failure</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Verify probe_redis catches connection failures and safely returns False</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>TC-122</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>P3-3</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>tests/unit/test_rate_limit.py</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>test_rate_limit_allows_requests_under_ceiling</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Verify requests under limit succeed with X-RateLimit-Limit and Remaining headers</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>TC-123</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>P3-3</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>tests/unit/test_rate_limit.py</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>test_rate_limit_blocks_exceeding_ceiling_returns_429</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Verify requests exceeding ceiling return HTTP 429 with Retry-After (N2)</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>TC-124</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>P3-3</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>tests/unit/test_rate_limit.py</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>test_rate_limit_isolates_different_client_ips</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Verify rate limit partitions counters by client IP address</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>TC-125</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>P3-3</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>tests/unit/test_rate_limit.py</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>test_rate_limit_exempts_health_endpoints</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Verify system health probes (/health/live) bypass rate limit enforcement</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>TC-126</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>P3-3</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>tests/unit/test_rate_limit.py</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>test_rate_limit_exempts_options_preflight</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Verify CORS OPTIONS preflight requests bypass rate limit counting</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>TC-127</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>P3-3</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>tests/unit/test_rate_limit.py</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>test_rate_limit_fails_open_on_redis_error</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Penetration test: verify middleware fails open during Redis outage (CWE-755)</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/TEST_CASES.xlsx
+++ b/docs/TEST_CASES.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Cases" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Test Cases" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G128"/>
+  <dimension ref="A1:G134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5208,6 +5208,228 @@
         </is>
       </c>
     </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>TC-128</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>P3-4</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>tests/unit/test_audit_middleware.py</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>test_audit_records_post_request</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>POST request generates immutable audit log record with actor, client IP, route, and status code (AC-068)</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>TC-129</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>P3-4</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>tests/unit/test_audit_middleware.py</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>test_audit_records_put_patch_delete_requests</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>PUT, PATCH, and DELETE operations are captured in audit_logs table (AC-068)</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>TC-130</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>P3-4</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>tests/unit/test_audit_middleware.py</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>test_audit_ignores_get_request</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>GET, HEAD, and OPTIONS requests are strictly excluded from audit_logs to prevent database bloat (AC-069)</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>TC-131</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>P3-4</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>tests/unit/test_audit_middleware.py</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>test_audit_extracts_authenticated_actor_id</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Extracts authenticated actor UUID from Authorization Bearer JWT claim or falls back to unauthenticated</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>TC-132</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>P3-4</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>tests/unit/test_audit_middleware.py</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>test_audit_fails_safe_on_database_error</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Penetration test: Audit database write failure fails safe without failing client HTTP response (CWE-755)</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>TC-133</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>P3-4</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>tests/unit/test_audit_middleware.py</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>test_main_application_middleware_stack_order</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Verify strict middleware stack ordering: CORS (outermost) -&gt; RequestId -&gt; RateLimit -&gt; Audit (innermost)</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/TEST_CASES.xlsx
+++ b/docs/TEST_CASES.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G134"/>
+  <dimension ref="A1:G163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5430,6 +5430,1079 @@
         </is>
       </c>
     </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>TC-134</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>P4-1</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>tests/unit/test_schemas_contract.py</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>test_ticket_create_valid_defaults</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Verify TicketCreate initializes with valid inputs and default channel=email (AC-001)</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>TC-135</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>P4-1</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>tests/unit/test_schemas_contract.py</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>test_ticket_create_all_supported_channels</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Verify all canonical channels (email, chat, web, api) are accepted (AC-001)</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>TC-136</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>P4-1</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>tests/unit/test_schemas_contract.py</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>test_ticket_create_rejects_invalid_channel</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Verify invalid channels like sms or phone raise validation error (AC-002)</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>TC-137</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>P4-1</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>tests/unit/test_schemas_contract.py</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>test_ticket_create_rejects_empty_or_whitespace_subject</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Verify empty or whitespace-only subject is rejected with ValidationError (AC-002)</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>TC-138</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>P4-1</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>tests/unit/test_schemas_contract.py</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>test_ticket_create_subject_length_boundaries</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Verify subject min_length=3 and max_length=255 boundaries</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>TC-139</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>P4-1</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>tests/unit/test_schemas_contract.py</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>test_ticket_create_large_payload_unicode_and_emojis</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Verify body handles up to 50,000 characters with unicode and emojis (AC-004)</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>TC-140</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>P4-1</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>tests/unit/test_schemas_contract.py</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>test_ticket_create_rejects_oversized_body</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Verify body exceeding 50,000 characters is rejected with ValidationError</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>TC-141</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>P4-1</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>tests/unit/test_schemas_contract.py</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>test_ticket_create_forbids_extra_fields</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Verify unexpected fields are rejected to prevent mass-assignment attacks</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Security Unit</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>TC-142</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>P4-1</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>tests/unit/test_schemas_contract.py</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>test_ticket_message_create_and_response</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Verify TicketMessageCreate and TicketMessageResponse serialization</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>TC-143</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>P4-1</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>tests/unit/test_schemas_contract.py</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>test_ticket_summary_response_serialization</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Verify TicketSummaryResponse serialization with all required status and severity fields</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>TC-144</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>P4-1</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>tests/unit/test_schemas_contract.py</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>test_ticket_detail_response_with_messages_and_customer</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Verify TicketDetailResponse aggregates messages and customer dossier references</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>TC-145</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>P4-1</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>tests/unit/test_schemas_contract.py</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>test_ticket_filter_params_validation</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Verify TicketFilterParams accepts valid enums and pagination boundaries (AC-007)</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>TC-146</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>P4-1</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>tests/unit/test_schemas_contract.py</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>test_ticket_filter_params_rejects_invalid_enums</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Verify invalid enum query parameters raise ValidationError (AC-008)</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>TC-147</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>P4-1</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>tests/unit/test_schemas_contract.py</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>test_ticket_list_response_empty_and_populated</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Verify TicketListResponse serializes empty list as [] and total: 0 (AC-009)</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>TC-148</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>P4-1</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>tests/unit/test_schemas_contract.py</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>test_workflow_run_response</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Verify WorkflowRunResponse serializes ticket_id, workflow_id, and 202 status</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>TC-149</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>P4-1</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>tests/unit/test_schemas_contract.py</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>test_workflow_state_response</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Verify WorkflowStateResponse contains completed_nodes, telemetry, and diagnostics</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>TC-150</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>P4-1</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>tests/unit/test_schemas_contract.py</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>test_workflow_event_response</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Verify WorkflowEventResponse captures node telemetry, timing, and token metrics (F13)</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>TC-151</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>P4-1</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>tests/unit/test_schemas_contract.py</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>test_reply_create_and_response</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Verify ReplyCreate validates body and ReplyResponse reflects dispatch status (AC-052)</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>TC-152</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>P4-1</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>tests/unit/test_schemas_contract.py</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>test_request_info_create</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Verify RequestInfoCreate validates question length</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>TC-153</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>P4-1</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>tests/unit/test_schemas_contract.py</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>test_escalate_request_and_response</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Verify EscalateRequest enforces target_team, policy_reason, and severity</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>TC-154</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>P4-1</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>tests/unit/test_schemas_contract.py</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>test_customer_create_and_update</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Verify CustomerCreate validates email and CustomerUpdate handles partial fields</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>TC-155</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>P4-1</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>tests/unit/test_schemas_contract.py</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>test_customer_summary_and_list_response</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Verify CustomerSummaryResponse and CustomerListResponse serialization</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>TC-156</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>P4-1</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>tests/unit/test_schemas_contract.py</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>test_customer_detail_response_aggregates_context</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Verify CustomerDetailResponse aggregates subscriptions, workspaces, tickets, and memory (AC-020)</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>TC-157</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>P4-1</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>tests/unit/test_schemas_contract.py</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>test_customer_memory_create_and_validation</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Verify CustomerMemoryCreate validates memory_type enum and content length</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>TC-158</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>P4-1</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>tests/unit/test_schemas_contract.py</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>test_customer_detail_bounds_memory_notes_to_ten</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Verify memory_notes field validator enforces the 10 most recent notes limit (AC-022)</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>TC-159</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>P4-1</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>tests/unit/test_schemas_contract.py</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>test_security_schema_sanitizes_or_encapsulates_xss</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Penetration test: XSS script tags in subject and body are preserved safely without escaping hazards</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>TC-160</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>P4-1</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>tests/unit/test_schemas_contract.py</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>test_security_schema_handles_sql_injection_strings</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Penetration test: SQL injection sequences in search and filter inputs are treated as literal strings</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>TC-161</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>P4-1</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>tests/unit/test_schemas_contract.py</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>test_security_schema_prototype_pollution_resistance</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Penetration test: Schema rejects prototype/attribute pollution keys (__proto__, __class__)</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>TC-162</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>P4-1</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>tests/unit/test_schemas_contract.py</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>test_role_enum_values_match_contract</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Verify role enum values match contract specifications (viewer, agent, admin)</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/TEST_CASES.xlsx
+++ b/docs/TEST_CASES.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G163"/>
+  <dimension ref="A1:G191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6503,6 +6503,1042 @@
         </is>
       </c>
     </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>TC-163</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>P4-2</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>tests/api/test_tickets.py</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>test_create_ticket_success_ac_001</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Verify POST /api/v1/tickets creates a ticket and initial message atomically (AC-001)</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>TC-164</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>P4-2</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>tests/api/test_tickets.py</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>test_create_ticket_all_supported_channels</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Verify ticket ingestion succeeds across all canonical channels (AC-001)</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>TC-165</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>P4-2</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>tests/api/test_tickets.py</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>test_create_ticket_invalid_channel_rejected_ac_002</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Verify invalid channel returns 422 Unprocessable Entity (AC-002)</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>TC-166</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>P4-2</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>tests/api/test_tickets.py</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>test_create_ticket_empty_or_whitespace_subject_rejected_ac_002</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Verify empty or whitespace-only subject returns 422 (AC-002)</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>TC-167</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>P4-2</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>tests/api/test_tickets.py</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>test_create_ticket_nonexistent_customer_returns_404_ac_003</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Verify referencing a non-existent customer_id returns HTTP 404 (AC-003)</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>TC-168</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>P4-2</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>tests/api/test_tickets.py</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>test_create_ticket_large_unicode_body_ac_004</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Verify body handles 50,000 characters with unicode and emojis without corruption (AC-004)</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>TC-169</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>P4-2</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>tests/api/test_tickets.py</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>test_create_ticket_oversized_body_rejected</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Verify bodies exceeding 50,000 characters are rejected with 422</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>TC-170</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>P4-2</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>tests/api/test_tickets.py</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>test_create_ticket_extra_fields_rejected_mass_assignment</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Verify extra/unknown parameters return 422 preventing mass assignment (CWE-915)</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>TC-171</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>P4-2</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>tests/api/test_tickets.py</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>test_list_tickets_unauthenticated_returns_401_ac_010</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Verify GET /api/v1/tickets without authorization token returns 401 Unauthorized (AC-010)</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>TC-172</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>P4-2</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>tests/api/test_tickets.py</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>test_list_tickets_all_roles_authorized_ac_011</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Verify viewer, agent, and admin roles can all view the ticket queue (AC-011)</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>TC-173</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>P4-2</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>tests/api/test_tickets.py</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>test_list_tickets_filtering_by_status_and_severity_ac_007</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Verify queue filtering by status and severity returns matching subset (AC-007)</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>TC-174</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>P4-2</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>tests/api/test_tickets.py</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>test_list_tickets_filtering_by_category_and_plan_ac_007</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Verify queue filtering by category and customer plan (AC-007)</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>TC-175</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>P4-2</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>tests/api/test_tickets.py</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>test_list_tickets_invalid_enum_returns_422_ac_008</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Verify invalid enum parameters return 422 Unprocessable Entity (AC-008)</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>TC-176</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>P4-2</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>tests/api/test_tickets.py</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>test_list_tickets_zero_match_returns_empty_list_ac_009</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Verify valid criteria with zero matches returns 200 with [] and total: 0 (AC-009)</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>TC-177</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>P4-2</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>tests/api/test_tickets.py</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>test_list_tickets_pagination</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Verify limit and offset pagination controls</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>TC-178</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>P4-2</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>tests/api/test_tickets.py</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>test_get_ticket_detail_success</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Verify GET /api/v1/tickets/{id} returns ticket dossier with chronological messages</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>TC-179</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>P4-2</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>tests/api/test_tickets.py</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>test_get_ticket_detail_not_found</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Verify non-existent ticket ID returns 404 Not Found</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>TC-180</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>P4-2</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>tests/api/test_tickets.py</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>test_get_ticket_detail_unauthenticated</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Verify unauthenticated GET /api/v1/tickets/{id} returns 401</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>TC-181</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>P4-2</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>tests/api/test_tickets.py</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>test_agent_reply_success_ac_052</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Verify agent can dispatch reply, appending message and setting waiting_on_customer (AC-052)</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>TC-182</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>P4-2</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>tests/api/test_tickets.py</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>test_viewer_reply_forbidden_rbac</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Verify viewer role is strictly forbidden from dispatching replies (HTTP 403)</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>TC-183</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>P4-2</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>tests/api/test_tickets.py</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>test_reply_blank_message_rejected</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Verify blank or whitespace-only reply message returns 422</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>TC-184</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>P4-2</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>tests/api/test_tickets.py</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>test_reply_nonexistent_ticket_returns_404</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Verify replying to non-existent ticket returns 404</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>TC-185</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>P4-2</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>tests/api/test_tickets.py</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>test_request_info_success_ac_054</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Verify agent can request clarification, appending message and setting waiting_on_customer (AC-054)</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>TC-186</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>P4-2</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>tests/api/test_tickets.py</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>test_viewer_request_info_forbidden_rbac</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Verify viewer role is forbidden from requesting clarification (HTTP 403)</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>TC-187</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>P4-2</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>tests/api/test_tickets.py</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>test_escalate_ticket_success_ac_045</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Verify agent can escalate ticket to target team with policy reason (AC-045)</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>TC-188</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>P4-2</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>tests/api/test_tickets.py</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>test_viewer_escalate_forbidden_rbac</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Verify viewer role is forbidden from escalating tickets (HTTP 403)</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>TC-189</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>P4-2</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>tests/api/test_tickets.py</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>test_security_xss_injection_contained_as_data_n4</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Penetration test: XSS payload in ticket body is stored safely as untrusted data without execution (N4)</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>TC-190</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>P4-2</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>tests/api/test_tickets.py</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>test_security_sql_injection_in_ticket_filters_safe</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Penetration test: SQL injection in customer_id filter parameter is parameterized safely (CWE-89)</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/TEST_CASES.xlsx
+++ b/docs/TEST_CASES.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G191"/>
+  <dimension ref="A1:G212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7539,6 +7539,783 @@
         </is>
       </c>
     </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>TC-191</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>P4-3</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>tests/api/test_customers.py</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>test_list_customers_unauthenticated_returns_401</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Verify GET /api/v1/customers without authorization returns 401 Unauthorized.</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>API / Integration</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>TC-192</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>P4-3</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>tests/api/test_customers.py</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>test_list_customers_all_roles_authorized</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Verify viewer, agent, and admin can all list customer records.</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>API / Integration</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>TC-193</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>P4-3</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>tests/api/test_customers.py</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>test_list_customers_filter_by_plan</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Verify filtering customers by subscription plan tier ('enterprise', 'pro', 'free').</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>API / Integration</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>TC-194</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>P4-3</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>tests/api/test_customers.py</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>test_list_customers_invalid_plan_returns_422</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Verify invalid plan query parameter returns 422 Unprocessable Entity.</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>API / Integration</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>TC-195</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>P4-3</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>tests/api/test_customers.py</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>test_list_customers_pagination</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Verify pagination limit and offset controls.</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>API / Integration</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>TC-196</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>P4-3</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>tests/api/test_customers.py</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>test_get_customer_dossier_success_ac_020</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Verify GET /api/v1/customers/{id} aggregates 360 dossier with context (AC-020).</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>API / Integration</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>TC-197</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>P4-3</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>tests/api/test_customers.py</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>test_get_customer_dossier_not_found</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Verify non-existent customer ID returns HTTP 404 Not Found.</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>API / Integration</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>TC-198</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>P4-3</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>tests/api/test_customers.py</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>test_get_customer_dossier_unauthenticated</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Verify unauthenticated request to customer dossier returns 401.</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>API / Integration</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>TC-199</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>P4-3</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>tests/api/test_customers.py</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>test_customer_context_strict_isolation_ac_023</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Verify queries filter strictly on customer ID without leaking other customers' data (AC-023).</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>API / Integration</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>TC-200</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>P4-3</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>tests/api/test_customers.py</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>test_add_customer_memory_success_ac_056</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Verify agent can add permanent memory note, visible in subsequent dossier lookups (AC-056).</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>API / Integration</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>TC-201</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>P4-3</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>tests/api/test_customers.py</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>test_add_customer_memory_scrubs_secrets_n7</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Verify secrets (credit cards, API keys, passwords) are scrubbed before storage (N7 / US-022).</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>API / Integration</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>TC-202</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>P4-3</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>tests/api/test_customers.py</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>test_viewer_add_memory_forbidden_rbac</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Verify viewer role is strictly forbidden from recording memory notes (HTTP 403).</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>TC-203</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>P4-3</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>tests/api/test_customers.py</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>test_add_memory_nonexistent_customer_returns_404</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Verify adding memory to non-existent customer returns 404.</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>API / Integration</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>TC-204</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>P4-3</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>tests/api/test_customers.py</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>test_add_memory_empty_content_rejected</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Verify empty or whitespace-only memory note content returns 422.</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>API / Integration</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>TC-205</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>P4-3</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>tests/api/test_customers.py</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>test_customer_dossier_bounds_memory_notes_to_ten_ac_022</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Verify customer dossier strictly limits recalled memory notes to 10 (AC-022).</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>API / Integration</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>TC-206</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>P4-3</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>tests/api/test_customers.py</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>test_list_customer_memory_notes_endpoint</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Verify dedicated GET /api/v1/customers/{id}/memory lists customer memory notes.</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>API / Integration</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>TC-207</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>P4-3</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>tests/api/test_customers.py</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>test_create_customer_success</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Verify agent can create a new customer entity.</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>API / Integration</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>TC-208</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>P4-3</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>tests/api/test_customers.py</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>test_create_customer_duplicate_email_conflict</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Verify registering duplicate customer email returns HTTP 409 Conflict.</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>API / Integration</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>TC-209</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>P4-3</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>tests/api/test_customers.py</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>test_viewer_create_customer_forbidden_rbac</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Verify viewer role is forbidden from registering new customers (HTTP 403).</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>TC-210</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>P4-3</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>tests/api/test_customers.py</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>test_security_sql_injection_in_customer_filters</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Penetration test: SQL injection in plan query parameter is rejected by enum validation (CWE-89).</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>TC-211</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>P4-3</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>tests/api/test_customers.py</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>test_security_xss_in_customer_memory_stored_safely</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Penetration test: XSS script in memory note is encapsulated as plain text data without execution (CWE-79).</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/TEST_CASES.xlsx
+++ b/docs/TEST_CASES.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G212"/>
+  <dimension ref="A1:G231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8316,6 +8316,709 @@
         </is>
       </c>
     </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>TC-212</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>P5-1</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>tests/rag/test_chunking.py</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>test_load_article_files_loads_all_15_articles</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Verify load_article_files loads exactly 15 articles from sample_data/knowledge_base.</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Unit / Pipeline</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>TC-213</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>P5-1</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>tests/rag/test_chunking.py</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>test_load_article_files_default_path</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Verify load_article_files without arguments defaults to sample_data/knowledge_base.</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Unit / Pipeline</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>TC-214</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>P5-1</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>tests/rag/test_chunking.py</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>test_load_article_files_nonexistent_directory</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Verify load_article_files raises FileNotFoundError for missing directory.</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Unit / Pipeline</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>TC-215</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>P5-1</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>tests/rag/test_chunking.py</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>test_load_single_article_file</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Verify load_article_file parses front-matter and content of a single markdown file.</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Unit / Pipeline</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>TC-216</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>P5-1</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>tests/rag/test_chunking.py</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>test_load_article_file_malformed_frontmatter</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Verify files without valid front-matter delimiters raise ValueError.</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Unit / Pipeline</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>TC-217</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>P5-1</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>tests/rag/test_chunking.py</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>test_chunk_article_splits_on_markdown_headings</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Verify chunk_article splits article into sections based on markdown headings.</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Unit / Pipeline</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>TC-218</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>P5-1</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>tests/rag/test_chunking.py</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>test_chunk_article_prefixes_with_title_and_heading</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Verify every chunk is prefixed with '{title} - {heading}' (CLAUDE.md spec).</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Unit / Pipeline</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>TC-219</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>P5-1</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>tests/rag/test_chunking.py</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>test_chunk_article_canonical_source_uri_format</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Verify chunk source follows 'kb://slug#section' format (CLAUDE.md spec).</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Unit / Pipeline</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>TC-220</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>P5-1</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>tests/rag/test_chunking.py</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>test_slugify_heading</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Verify slugify_heading produces valid URL anchor slugs.</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Unit / Pipeline</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>TC-221</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>P5-1</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>tests/rag/test_chunking.py</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>test_chunk_section_under_900_chars_is_single_chunk</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Verify sections with &lt;= 900 characters produce exactly one chunk without windowing.</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Unit / Pipeline</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>TC-222</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>P5-1</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>tests/rag/test_chunking.py</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>test_chunk_section_over_900_chars_windows_with_150_overlap</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Verify sections &gt; 900 chars slide a 900-char window with 150-char overlap.</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Unit / Pipeline</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>TC-223</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>P5-1</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>tests/rag/test_chunking.py</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>test_chunk_article_no_headings_falls_back_to_overview</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Verify article without any '#' headings chunks cleanly under 'Overview'.</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Unit / Pipeline</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>TC-224</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>P5-1</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>tests/rag/test_chunking.py</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>test_chunk_article_empty_or_whitespace_ignored</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Verify empty sections or articles with no body return empty chunk lists.</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Unit / Pipeline</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>TC-225</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>P5-1</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>tests/rag/test_chunking.py</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>test_chunk_all_15_sample_articles</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Verify batch chunking of all 15 sample articles produces valid chunks.</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Unit / Pipeline</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>TC-226</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>P5-1</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>tests/rag/test_chunking.py</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>test_chunk_to_evidence_dict_compatibility</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Verify ArticleChunk can convert to the exact Evidence shape required by agents (CLAUDE.md §8).</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>Unit / Pipeline</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>TC-227</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>P5-1</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>tests/rag/test_chunking.py</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>test_chunking_is_deterministic</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Verify re-running chunking on the same article produces identical chunk IDs and hashes.</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>Unit / Pipeline</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>TC-228</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>P5-1</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>tests/rag/test_chunking.py</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>test_security_path_traversal_in_article_loader</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Penetration test: Attempting path traversal outside allowed directory is blocked (CWE-22).</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>TC-229</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>P5-1</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>tests/rag/test_chunking.py</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>test_security_malicious_markdown_parsing_safe</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Penetration test: HTML script tags or XXE payloads in markdown are parsed safely as text (CWE-79).</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>TC-230</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>P5-1</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>tests/rag/test_chunking.py</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>test_security_no_secrets_in_sample_kb_articles</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Penetration test: Verify no sample KB article contains live API keys, card numbers, or passwords.</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/TEST_CASES.xlsx
+++ b/docs/TEST_CASES.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G231"/>
+  <dimension ref="A1:G249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9019,6 +9019,672 @@
         </is>
       </c>
     </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>TC-231</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>P5-2</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>tests/rag/test_vector_store.py</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>test_fake_embeddings_dimensions</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Verify FakeEmbeddings generates vectors with exact dimensions (default 384) and unit norm.</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Unit / VectorStore</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>TC-232</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>P5-2</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>tests/rag/test_vector_store.py</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>test_fake_embeddings_deterministic</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Verify embedding the same string repeatedly produces identical vectors.</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Unit / VectorStore</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>TC-233</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>P5-2</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>tests/rag/test_vector_store.py</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>test_fake_embeddings_semantic_similarity</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Verify texts sharing vocabulary have higher cosine similarity than unrelated texts.</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Unit / VectorStore</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>TC-234</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>P5-2</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>tests/rag/test_vector_store.py</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>test_fake_embeddings_empty_string_safe</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Verify empty or whitespace-only strings produce a zero or safe unit vector without division error.</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Unit / VectorStore</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>TC-235</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>P5-2</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>tests/rag/test_vector_store.py</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>test_fake_embeddings_batch_embedding</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Verify embed_documents returns vectors for all input texts in batch.</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Unit / VectorStore</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>TC-236</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>P5-2</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>tests/rag/test_vector_store.py</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>test_in_memory_vector_store_add_and_count</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Verify adding documents to InMemoryVectorStore increments document count.</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Unit / VectorStore</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>TC-237</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>P5-2</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>tests/rag/test_vector_store.py</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>test_in_memory_vector_store_search_top_k</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Verify search returns top_k documents sorted by similarity score descending.</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Unit / VectorStore</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>TC-238</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>P5-2</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>tests/rag/test_vector_store.py</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>test_in_memory_vector_store_search_with_metadata_filter</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Verify metadata filtering restricts results to matching categories.</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>Unit / VectorStore</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>TC-239</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>P5-2</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>tests/rag/test_vector_store.py</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>test_in_memory_vector_store_delete</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Verify delete removes documents by ID and updates count.</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>Unit / VectorStore</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>TC-240</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>P5-2</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>tests/rag/test_vector_store.py</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>test_in_memory_vector_store_clear</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Verify clear purges all indexed documents.</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>Unit / VectorStore</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>TC-241</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>P5-2</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>tests/rag/test_vector_store.py</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>test_in_memory_vector_store_health</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>Verify health endpoint reports store status, provider, and document count.</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>Unit / VectorStore</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>TC-242</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>P5-2</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>tests/rag/test_vector_store.py</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>test_index_article_chunks_directly</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>Verify InMemoryVectorStore accepts ArticleChunk instances from chunking pipeline directly.</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>Unit / VectorStore</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>TC-243</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>P5-2</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>tests/rag/test_vector_store.py</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>test_vector_search_result_to_evidence_format</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>Verify VectorSearchResult formats into the required Evidence dictionary shape (CLAUDE.md §8).</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>Unit / VectorStore</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>TC-244</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>P5-2</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>tests/rag/test_vector_store.py</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>test_get_vector_store_memory_default</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>Verify get_vector_store() returns InMemoryVectorStore when VECTOR_STORE='memory'.</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>Unit / VectorStore</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>TC-245</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>P5-2</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>tests/rag/test_vector_store.py</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>test_get_vector_store_protocol_compliance</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>Verify returned store adheres to VectorStoreService protocol.</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>Unit / VectorStore</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>TC-246</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>P5-2</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>tests/rag/test_vector_store.py</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>test_security_vector_search_injection_safe</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>Penetration test: SQL/NoSQL injection payloads in query strings execute safely as vector embeddings (CWE-89).</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>TC-247</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>P5-2</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>tests/rag/test_vector_store.py</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>test_security_massive_input_embedding_bounds</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>Penetration test: Massive input text (50,000 chars) embeds within memory limits without DoS (CWE-400).</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>TC-248</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>P5-2</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>tests/rag/test_vector_store.py</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>test_security_metadata_isolation</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Penetration test: Documents with prototype pollution attempts do not corrupt store internals.</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/TEST_CASES.xlsx
+++ b/docs/TEST_CASES.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G249"/>
+  <dimension ref="A1:G266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9685,6 +9685,635 @@
         </is>
       </c>
     </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>TC-249</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>P5-3</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>tests/rag/test_retriever.py</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>test_hybrid_retriever_initialization</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>Verify retriever instantiates with defaults and builds vector/BM25 structures.</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>Unit / Retriever</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>TC-250</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>P5-3</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>tests/rag/test_retriever.py</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>test_retriever_index_corpus</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>Verify index_corpus populates both vector store and BM25 index.</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>Unit / Retriever</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>TC-251</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>P5-3</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>tests/rag/test_retriever.py</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>test_hybrid_retrieval_mode</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>Verify default hybrid mode combines semantic and keyword scores into valid evidence shape.</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>Integration / Retriever</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>TC-252</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>P5-3</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>tests/rag/test_retriever.py</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>test_semantic_retrieval_mode</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>Verify semantic mode executes purely against vector store.</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>Unit / Retriever</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>TC-253</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>P5-3</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>tests/rag/test_retriever.py</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>test_keyword_retrieval_mode</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>Verify keyword mode executes purely against BM25 index.</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>Unit / Retriever</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>TC-254</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>P5-3</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>tests/rag/test_retriever.py</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>test_invalid_retrieval_mode_raises</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>Verify invalid mode parameter raises ValueError.</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>Unit / Retriever</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>TC-255</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>P5-3</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>tests/rag/test_retriever.py</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>test_deduplication_one_hit_per_article</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>Verify strictly one hit per article is returned (CLAUDE.md §8).</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>Unit / Retriever</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>TC-256</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>P5-3</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>tests/rag/test_retriever.py</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>test_category_boost_heuristics</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>Verify category match provides a 1.35x boost to candidate scores.</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>Unit / Retriever</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>TC-257</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>P5-3</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>tests/rag/test_retriever.py</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>test_reciprocal_rank_fusion_logic</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>Verify RRF formula k=60 computes higher score when an item ranks high across both signals.</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>Unit / Retriever</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>TC-258</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>P5-3</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>tests/rag/test_retriever.py</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>test_redis_retrieval_caching</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>Verify results are cached in Redis under rag:{mode}:{category}:{top_k}:{query} with 300s TTL.</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>Integration / Cache</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>TC-259</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>P5-3</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>tests/rag/test_retriever.py</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>test_redis_cache_bypass</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>Verify use_cache=False bypasses Redis lookup and write.</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>Integration / Cache</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>TC-260</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>P5-3</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>tests/rag/test_retriever.py</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>test_redis_graceful_degradation_on_error</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>Verify retriever falls back gracefully to live retrieval if Redis raises an error.</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>Integration / Cache</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>TC-261</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>P5-3</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>tests/rag/test_retriever.py</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>test_quality_bar_hit_rate_at_3</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>Verify retrieval hit-rate@3 is &gt;= 0.75 across the 13 reference sample tickets.</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>Evaluation / Benchmark</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>TC-262</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>P5-3</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>tests/rag/test_retriever.py</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>test_security_sql_and_nosql_injection_query_containment</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>Penetration test: SQL and NoSQL injection payloads in query execute safely (CWE-89 / CWE-943).</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>TC-263</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>P5-3</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>tests/rag/test_retriever.py</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>test_security_xss_in_evidence_snippet</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>Penetration test: Stored/reflected XSS script in query or content is handled safely (CWE-79).</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>TC-264</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>P5-3</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>tests/rag/test_retriever.py</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>test_security_redos_query_safety</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>Penetration test: Extremely large repetitive input terminates in bounded time without ReDoS (CWE-1333).</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>TC-265</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>P5-3</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>tests/rag/test_retriever.py</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>test_security_cache_key_poisoning_containment</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>Penetration test: Carriage return and newline injection in query cannot poison Redis protocol (CWE-93).</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/TEST_CASES.xlsx
+++ b/docs/TEST_CASES.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G266"/>
+  <dimension ref="A1:G288"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10314,6 +10314,820 @@
         </is>
       </c>
     </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>TC-266</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>P5-4</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>tests/rag/test_ingest.py</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>test_ingest_knowledge_base_success</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>Verify ingest_knowledge_base loads 15 articles, produces chunks, and indexes into vector store.</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>Unit / Ingest</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>TC-267</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>P5-4</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>tests/rag/test_ingest.py</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>test_ingest_knowledge_base_recreate</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>Verify recreate=True purges previous vector store contents before re-indexing.</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>Unit / Ingest</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>TC-268</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>P5-4</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>tests/rag/test_ingest.py</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>test_ingest_knowledge_base_empty_dir</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>Verify ingesting an empty directory returns zero articles and zero chunks safely.</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>Unit / Ingest</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>TC-269</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>P5-4</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>tests/rag/test_ingest.py</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>test_ingest_knowledge_base_idempotent</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>Verify calling ingest_knowledge_base multiple times is idempotent.</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>Unit / Ingest</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>TC-270</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>P5-4</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>tests/rag/test_ingest.py</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>test_ingest_cli_main_success</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>Verify CLI main entrypoint executes with zero exit code and logs counts.</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>CLI / Ingest</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>TC-271</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>P5-4</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>tests/api/test_knowledge.py</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>test_knowledge_search_as_viewer</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>Verify viewer can perform hybrid search and receives canonical Evidence hits.</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>Integration / API</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>TC-272</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>P5-4</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>tests/api/test_knowledge.py</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>test_knowledge_search_as_agent</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>Verify agent can search knowledge base.</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>Integration / API</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>TC-273</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>P5-4</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>tests/api/test_knowledge.py</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>test_knowledge_search_as_unauthenticated_fails</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>Verify unauthenticated search fails with 401 Unauthorized.</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>Security / RBAC</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>TC-274</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>P5-4</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>tests/api/test_knowledge.py</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>test_knowledge_search_pure_modes</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>Verify semantic and keyword modes execute without error.</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>Integration / API</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>TC-275</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>P5-4</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>tests/api/test_knowledge.py</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>test_knowledge_search_invalid_mode_rejected</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>Verify invalid mode returns 422 Unprocessable Entity.</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>Validation / API</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>TC-276</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>P5-4</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>tests/api/test_knowledge.py</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>test_knowledge_search_empty_query_rejected</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>Verify empty query string returns 422 Unprocessable Entity.</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>Validation / API</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>TC-277</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>P5-4</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>tests/api/test_knowledge.py</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>test_knowledge_search_invalid_top_k_bounds</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>Verify top_k &lt;= 0 or top_k &gt; 20 returns 422.</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>Validation / API</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>TC-278</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>P5-4</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>tests/api/test_knowledge.py</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>test_knowledge_reindex_as_admin_success</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>Verify admin role can trigger reindex and receives article/chunk counts (API_CONTRACT.md §5.2).</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>Integration / API</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>TC-279</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>P5-4</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>tests/api/test_knowledge.py</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>test_knowledge_reindex_as_viewer_forbidden</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>Verify viewer cannot trigger reindex (403 Forbidden).</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>Security / RBAC</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>TC-280</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>P5-4</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>tests/api/test_knowledge.py</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>test_knowledge_reindex_as_agent_forbidden</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>Verify agent cannot trigger reindex (403 Forbidden).</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>Security / RBAC</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>TC-281</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>P5-4</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>tests/api/test_knowledge.py</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>test_list_knowledge_articles_as_viewer</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>Verify viewer can list knowledge base articles.</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>Integration / API</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>TC-282</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>P5-4</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>tests/api/test_knowledge.py</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>test_get_knowledge_article_by_slug</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>Verify retrieving article by slug returns detailed article with markdown content.</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>Integration / API</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>TC-283</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>P5-4</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>tests/api/test_knowledge.py</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>test_get_knowledge_article_by_art_id</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>Verify retrieving article by full art- ID format succeeds.</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>Integration / API</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>TC-284</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>P5-4</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>tests/api/test_knowledge.py</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>test_get_nonexistent_knowledge_article_404</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>Verify nonexistent article slug returns 404 Not Found.</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>Integration / API</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>TC-285</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>P5-4</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>tests/api/test_knowledge.py</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>test_security_sql_injection_in_search_query</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>Penetration test: SQL injection in search query executes safely without data leakage (CWE-89).</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>TC-286</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>P5-4</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>tests/api/test_knowledge.py</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>test_security_path_traversal_in_article_endpoint</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>Penetration test: Directory traversal attempts in article route return 404/422 without file leak (CWE-22).</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>TC-287</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>P5-4</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>tests/api/test_knowledge.py</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>test_security_xss_payload_in_query</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>Penetration test: XSS script tags in search query are handled as plain text (CWE-79).</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
